--- a/project_submission/Member Contribution/2025-2026-HK3-Group02-Project Evaluation.xlsx
+++ b/project_submission/Member Contribution/2025-2026-HK3-Group02-Project Evaluation.xlsx
@@ -32,62 +32,68 @@
     <t>02</t>
   </si>
   <si>
-    <t>PROJECT CONTRIBUTION</t>
-  </si>
-  <si>
-    <t>Number of students working in the project</t>
-  </si>
-  <si>
-    <t>Number of tasks</t>
-  </si>
-  <si>
-    <t>Number of task hours</t>
-  </si>
-  <si>
     <t>A task should be done by only 1-2 students. Duplicate tasks are not recommended
 Each member should work on at least 5 tasks</t>
   </si>
   <si>
+    <t>PROJECT CONTRIBUTION</t>
+  </si>
+  <si>
+    <t>Number of students working in the project</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Number of tasks</t>
+  </si>
+  <si>
+    <t>Student ID</t>
+  </si>
+  <si>
+    <t>Full name</t>
+  </si>
+  <si>
+    <t>Task Description</t>
+  </si>
+  <si>
+    <t>Hours</t>
+  </si>
+  <si>
+    <t>Evidence (screenshots of chat messages, of Git commits... proving that you perform and finish the task)</t>
+  </si>
+  <si>
+    <t>Võ Gia Minh</t>
+  </si>
+  <si>
+    <t>- Implemented camera system and map grids</t>
+  </si>
+  <si>
+    <t>https://github.com/khanh47/CS202_GameProject/commit/759dc80895dbc6084347f0b49f6a0ea76d48c093</t>
+  </si>
+  <si>
+    <t>Number of task hours</t>
+  </si>
+  <si>
     <t>Number of Git commits</t>
   </si>
   <si>
     <t>Max student percentage</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>Project score</t>
   </si>
   <si>
-    <t>Student ID</t>
-  </si>
-  <si>
-    <t>Full name</t>
-  </si>
-  <si>
-    <t>Task Description</t>
-  </si>
-  <si>
-    <t>Hours</t>
-  </si>
-  <si>
-    <t>Evidence (screenshots of chat messages, of Git commits... proving that you perform and finish the task)</t>
-  </si>
-  <si>
     <t>Do not edit the grey cells. TAs will enter the score of all PAs in the project score and get the individual scores. Students can enter an estimated project score to see how percentages affects your scores</t>
   </si>
   <si>
-    <t>Võ Gia Minh</t>
-  </si>
-  <si>
-    <t>- Implemented camera system and map grids</t>
+    <t>- Added fire state with ability to shoot fireballs</t>
   </si>
   <si>
     <t>Use columns Tasks - Percent, Task Hours - Percent, Git - Percent as references for column Percent</t>
   </si>
   <si>
-    <t>https://github.com/khanh47/CS202_GameProject/commit/759dc80895dbc6084347f0b49f6a0ea76d48c093</t>
+    <t>https://github.com/khanh47/CS202_GameProject/commit/c3e5f7602feec3e273de6529420ab6ce36bb9acc</t>
   </si>
   <si>
     <t>Tasks</t>
@@ -115,12 +121,6 @@
   </si>
   <si>
     <t>Score - TA</t>
-  </si>
-  <si>
-    <t>- Added fire state with ability to shoot fireballs</t>
-  </si>
-  <si>
-    <t>https://github.com/khanh47/CS202_GameProject/commit/c3e5f7602feec3e273de6529420ab6ce36bb9acc</t>
   </si>
   <si>
     <t>- Added super state and starman state</t>
@@ -706,6 +706,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="16.0"/>
       <color rgb="FFFFFFFF"/>
@@ -716,12 +722,6 @@
       <b/>
       <sz val="16.0"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -738,12 +738,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <color rgb="FF000000"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -817,54 +817,54 @@
     <xf quotePrefix="1" borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="9" xfId="0" applyFill="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="9" xfId="0" applyFill="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="2" numFmtId="9" xfId="0" applyFill="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="9" xfId="0" applyFill="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="9" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -872,7 +872,7 @@
     <xf borderId="0" fillId="4" fontId="2" numFmtId="9" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="11" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
@@ -891,16 +891,16 @@
     <xf borderId="0" fillId="5" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1172,6 +1172,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
@@ -1211,11 +1212,11 @@
       <c r="K3" s="3"/>
     </row>
     <row r="4" ht="39.0" customHeight="1">
-      <c r="A4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
+      <c r="A4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
     </row>
@@ -1225,9 +1226,9 @@
     </row>
     <row r="6">
       <c r="C6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="7">
+        <v>8</v>
+      </c>
+      <c r="D6" s="9">
         <v>4.0</v>
       </c>
       <c r="J6" s="3"/>
@@ -1235,9 +1236,9 @@
     </row>
     <row r="7">
       <c r="C7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="8">
+        <v>10</v>
+      </c>
+      <c r="D7" s="12">
         <f>SUM(D17:D24)</f>
         <v>48</v>
       </c>
@@ -1246,9 +1247,9 @@
     </row>
     <row r="8">
       <c r="C8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="8">
+        <v>19</v>
+      </c>
+      <c r="D8" s="12">
         <f>SUM(F17:F24)</f>
         <v>71.3</v>
       </c>
@@ -1257,20 +1258,20 @@
     </row>
     <row r="9">
       <c r="C9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="8">
+        <v>20</v>
+      </c>
+      <c r="D9" s="12">
         <f>SUM(H17:H24)</f>
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
     </row>
     <row r="10">
       <c r="C10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="11">
+        <v>21</v>
+      </c>
+      <c r="D10" s="13">
         <f>MAX((J17:J24))</f>
         <v>0.25</v>
       </c>
@@ -1278,10 +1279,10 @@
       <c r="K10" s="3"/>
     </row>
     <row r="11">
-      <c r="C11" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="14">
+      <c r="C11" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="15">
         <v>10.0</v>
       </c>
       <c r="J11" s="3"/>
@@ -1292,14 +1293,14 @@
       <c r="K12" s="3"/>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="s">
-        <v>20</v>
+      <c r="A13" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="K13" s="3"/>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="s">
-        <v>23</v>
+      <c r="A14" s="19" t="s">
+        <v>25</v>
       </c>
       <c r="K14" s="3"/>
     </row>
@@ -1308,73 +1309,73 @@
       <c r="K15" s="3"/>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="12" t="s">
+      <c r="A16" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="G16" s="12" t="s">
+      <c r="E16" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="F16" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="I16" s="12" t="s">
+      <c r="G16" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="J16" s="12" t="s">
+      <c r="H16" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="K16" s="12" t="s">
+      <c r="I16" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="L16" s="12" t="s">
+      <c r="J16" s="10" t="s">
         <v>33</v>
+      </c>
+      <c r="K16" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="10" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2">
         <v>1.0</v>
       </c>
-      <c r="B17" s="18">
+      <c r="B17" s="20">
         <v>2.512503E7</v>
       </c>
-      <c r="C17" s="18" t="s">
-        <v>21</v>
+      <c r="C17" s="20" t="s">
+        <v>16</v>
       </c>
       <c r="D17" s="2">
         <v>12.0</v>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="13">
         <f t="shared" ref="E17:E20" si="1">IF($D$7=0, 0, D17/$D$7)</f>
         <v>0.25</v>
       </c>
       <c r="F17" s="2">
         <v>16.0</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="13">
         <f t="shared" ref="G17:G20" si="2">IF($D$8=0, 0, F17/$D$8)</f>
         <v>0.2244039271</v>
       </c>
       <c r="H17" s="2">
         <v>67.0</v>
       </c>
-      <c r="I17" s="21">
+      <c r="I17" s="22">
         <f t="shared" ref="I17:I19" si="3">if($D$9 = 0, 0, H17/$D$9)</f>
-        <v>0.285106383</v>
+        <v>0.281512605</v>
       </c>
       <c r="J17" s="23">
         <v>0.25</v>
@@ -1383,22 +1384,22 @@
         <f t="shared" ref="K17:K20" si="4">if(J17=$D$10, $D$11, ROUND(2 * ($D$11 - 1 * $D$11 * (1-J17/$D$10)),0)/2)</f>
         <v>10</v>
       </c>
-      <c r="L17" s="8"/>
+      <c r="L17" s="12"/>
     </row>
     <row r="18">
       <c r="A18" s="2">
         <v>2.0</v>
       </c>
-      <c r="B18" s="18">
+      <c r="B18" s="20">
         <v>2.5125055E7</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="20" t="s">
         <v>42</v>
       </c>
       <c r="D18" s="2">
         <v>12.0</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="13">
         <f t="shared" si="1"/>
         <v>0.25</v>
       </c>
@@ -1406,16 +1407,16 @@
         <f>SUM(Tasks!E16:E28)</f>
         <v>16</v>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="13">
         <f t="shared" si="2"/>
         <v>0.2244039271</v>
       </c>
       <c r="H18" s="2">
-        <v>71.0</v>
-      </c>
-      <c r="I18" s="21">
+        <v>74.0</v>
+      </c>
+      <c r="I18" s="22">
         <f t="shared" si="3"/>
-        <v>0.3021276596</v>
+        <v>0.3109243697</v>
       </c>
       <c r="J18" s="23">
         <v>0.25</v>
@@ -1424,22 +1425,22 @@
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="L18" s="8"/>
+      <c r="L18" s="12"/>
     </row>
     <row r="19">
       <c r="A19" s="2">
         <v>3.0</v>
       </c>
-      <c r="B19" s="18">
+      <c r="B19" s="20">
         <v>2.5125066E7</v>
       </c>
-      <c r="C19" s="18" t="s">
+      <c r="C19" s="20" t="s">
         <v>45</v>
       </c>
       <c r="D19" s="2">
         <v>12.0</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="13">
         <f t="shared" si="1"/>
         <v>0.25</v>
       </c>
@@ -1447,16 +1448,16 @@
         <f>SUM(Tasks!E29:E40)</f>
         <v>23.3</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="13">
         <f t="shared" si="2"/>
         <v>0.3267882188</v>
       </c>
       <c r="H19" s="2">
         <v>38.0</v>
       </c>
-      <c r="I19" s="21">
+      <c r="I19" s="22">
         <f t="shared" si="3"/>
-        <v>0.1617021277</v>
+        <v>0.1596638655</v>
       </c>
       <c r="J19" s="23">
         <v>0.25</v>
@@ -1465,29 +1466,29 @@
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="L19" s="8"/>
+      <c r="L19" s="12"/>
     </row>
     <row r="20">
       <c r="A20" s="2">
         <v>4.0</v>
       </c>
-      <c r="B20" s="18">
+      <c r="B20" s="20">
         <v>2.5125085E7</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="20" t="s">
         <v>48</v>
       </c>
       <c r="D20" s="2">
         <v>12.0</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E20" s="13">
         <f t="shared" si="1"/>
         <v>0.25</v>
       </c>
       <c r="F20" s="2">
         <v>16.0</v>
       </c>
-      <c r="G20" s="11">
+      <c r="G20" s="13">
         <f t="shared" si="2"/>
         <v>0.2244039271</v>
       </c>
@@ -1504,17 +1505,17 @@
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="L20" s="8"/>
+      <c r="L20" s="12"/>
     </row>
     <row r="21">
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
     </row>
     <row r="22">
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
     </row>
@@ -5472,6 +5473,9 @@
     <mergeCell ref="A13:J13"/>
     <mergeCell ref="A14:J14"/>
   </mergeCells>
+  <printOptions gridLines="1" horizontalCentered="1"/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup fitToHeight="0" cellComments="atEnd" orientation="landscape" pageOrder="overThenDown"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -5480,6 +5484,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
@@ -5490,8 +5495,8 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="s">
-        <v>10</v>
+      <c r="A1" s="5" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="2">
@@ -5500,422 +5505,422 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="10"/>
+      <c r="F2" s="8"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="E3" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="12" t="s">
+    </row>
+    <row r="4">
+      <c r="A4" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="B4" s="11">
+        <v>2.512503E7</v>
+      </c>
+      <c r="C4" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E4" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="F4" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="B4" s="15">
-        <v>2.512503E7</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="15">
+    </row>
+    <row r="5">
+      <c r="A5" s="11">
+        <v>2.0</v>
+      </c>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="11">
         <v>0.5</v>
       </c>
-      <c r="F4" s="19" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="15">
+      <c r="F5" s="21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11">
+        <v>3.0</v>
+      </c>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11">
+        <v>4.0</v>
+      </c>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="11">
         <v>2.0</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="15">
+      <c r="F7" s="21" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11">
+        <v>5.0</v>
+      </c>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="11">
         <v>0.5</v>
       </c>
-      <c r="F5" s="22" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="15">
+      <c r="F8" s="21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11">
+        <v>6.0</v>
+      </c>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="11">
+        <v>2.0</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11">
+        <v>7.0</v>
+      </c>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="11">
+        <v>2.0</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11">
+        <v>8.0</v>
+      </c>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="F11" s="21" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11">
+        <v>9.0</v>
+      </c>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="11">
         <v>3.0</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="15">
+      <c r="F12" s="21" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11">
+        <v>10.0</v>
+      </c>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="11">
         <v>0.5</v>
       </c>
-      <c r="F6" s="22" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15">
-        <v>4.0</v>
-      </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" s="15">
+      <c r="F13" s="21" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11">
+        <v>11.0</v>
+      </c>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="11">
         <v>2.0</v>
       </c>
-      <c r="F7" s="22" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15">
-        <v>5.0</v>
-      </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" s="15">
+      <c r="F14" s="21" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11">
+        <v>12.0</v>
+      </c>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="11">
+        <v>2.0</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11">
+        <v>13.0</v>
+      </c>
+      <c r="B16" s="11">
+        <v>2.5125055E7</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="11">
         <v>0.5</v>
       </c>
-      <c r="F8" s="22" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="15">
-        <v>6.0</v>
-      </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="15">
-        <v>2.0</v>
-      </c>
-      <c r="F9" s="22" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="15">
-        <v>7.0</v>
-      </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" s="15">
-        <v>2.0</v>
-      </c>
-      <c r="F10" s="22" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15">
-        <v>8.0</v>
-      </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="F11" s="22" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="15">
-        <v>9.0</v>
-      </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" s="15">
-        <v>3.0</v>
-      </c>
-      <c r="F12" s="22" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="15">
-        <v>10.0</v>
-      </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="E13" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="F13" s="22" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="15">
-        <v>11.0</v>
-      </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="E14" s="15">
-        <v>2.0</v>
-      </c>
-      <c r="F14" s="22" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="15">
-        <v>12.0</v>
-      </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15" s="15">
-        <v>2.0</v>
-      </c>
-      <c r="F15" s="22" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15">
-        <v>13.0</v>
-      </c>
-      <c r="B16" s="15">
-        <v>2.5125055E7</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="E16" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="F16" s="22" t="s">
+      <c r="F16" s="21" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15">
+      <c r="A17" s="11">
         <v>14.0</v>
       </c>
       <c r="B17" s="26"/>
       <c r="C17" s="26"/>
-      <c r="D17" s="20" t="s">
+      <c r="D17" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="11">
         <v>0.5</v>
       </c>
-      <c r="F17" s="22" t="s">
+      <c r="F17" s="21" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15">
+      <c r="A18" s="11">
         <v>15.0</v>
       </c>
       <c r="B18" s="26"/>
       <c r="C18" s="26"/>
-      <c r="D18" s="20" t="s">
+      <c r="D18" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="11">
         <v>0.5</v>
       </c>
-      <c r="F18" s="22" t="s">
+      <c r="F18" s="21" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15">
+      <c r="A19" s="11">
         <v>16.0</v>
       </c>
       <c r="B19" s="26"/>
       <c r="C19" s="26"/>
-      <c r="D19" s="20" t="s">
+      <c r="D19" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="E19" s="15">
+      <c r="E19" s="11">
         <v>0.1</v>
       </c>
-      <c r="F19" s="22" t="s">
+      <c r="F19" s="21" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15">
+      <c r="A20" s="11">
         <v>17.0</v>
       </c>
       <c r="B20" s="26"/>
       <c r="C20" s="26"/>
-      <c r="D20" s="20" t="s">
+      <c r="D20" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="15">
+      <c r="E20" s="11">
         <v>2.0</v>
       </c>
-      <c r="F20" s="19" t="s">
+      <c r="F20" s="16" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15">
+      <c r="A21" s="11">
         <v>18.0</v>
       </c>
       <c r="B21" s="26"/>
       <c r="C21" s="26"/>
-      <c r="D21" s="20" t="s">
+      <c r="D21" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="E21" s="15">
+      <c r="E21" s="11">
         <v>4.0</v>
       </c>
-      <c r="F21" s="19" t="s">
+      <c r="F21" s="16" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15">
+      <c r="A22" s="11">
         <v>19.0</v>
       </c>
       <c r="B22" s="26"/>
       <c r="C22" s="26"/>
-      <c r="D22" s="20" t="s">
+      <c r="D22" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="E22" s="15">
+      <c r="E22" s="11">
         <v>1.5</v>
       </c>
-      <c r="F22" s="22" t="s">
+      <c r="F22" s="21" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="15">
+      <c r="A23" s="11">
         <v>20.0</v>
       </c>
       <c r="B23" s="26"/>
       <c r="C23" s="26"/>
-      <c r="D23" s="20" t="s">
+      <c r="D23" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="E23" s="15">
+      <c r="E23" s="11">
         <v>0.2</v>
       </c>
-      <c r="F23" s="22" t="s">
+      <c r="F23" s="21" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="15">
+      <c r="A24" s="11">
         <v>21.0</v>
       </c>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
       <c r="D24" s="27" t="s">
         <v>72</v>
       </c>
       <c r="E24" s="28">
         <v>1.0</v>
       </c>
-      <c r="F24" s="22" t="s">
+      <c r="F24" s="21" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15">
+      <c r="A25" s="11">
         <v>22.0</v>
       </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
       <c r="D25" s="29" t="s">
         <v>74</v>
       </c>
       <c r="E25" s="30">
         <v>0.5</v>
       </c>
-      <c r="F25" s="22" t="s">
+      <c r="F25" s="21" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15">
+      <c r="A26" s="11">
         <v>23.0</v>
       </c>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
       <c r="D26" s="31" t="s">
         <v>76</v>
       </c>
       <c r="E26" s="30">
         <v>0.2</v>
       </c>
-      <c r="F26" s="22" t="s">
+      <c r="F26" s="21" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15">
+      <c r="A27" s="11">
         <v>24.0</v>
       </c>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
       <c r="D27" s="29" t="s">
         <v>78</v>
       </c>
       <c r="E27" s="30">
         <v>1.0</v>
       </c>
-      <c r="F27" s="22" t="s">
+      <c r="F27" s="21" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15">
+      <c r="A28" s="11">
         <v>25.0</v>
       </c>
       <c r="B28" s="26"/>
@@ -5926,18 +5931,18 @@
       <c r="E28" s="32">
         <v>4.0</v>
       </c>
-      <c r="F28" s="19" t="s">
+      <c r="F28" s="16" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15">
+      <c r="A29" s="11">
         <v>26.0</v>
       </c>
-      <c r="B29" s="15">
+      <c r="B29" s="11">
         <v>2.5125066E7</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="11" t="s">
         <v>45</v>
       </c>
       <c r="D29" s="30" t="s">
@@ -5946,194 +5951,194 @@
       <c r="E29" s="30">
         <v>1.0</v>
       </c>
-      <c r="F29" s="22" t="s">
+      <c r="F29" s="21" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="15">
+      <c r="A30" s="11">
         <v>27.0</v>
       </c>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
       <c r="D30" s="30" t="s">
         <v>84</v>
       </c>
       <c r="E30" s="30">
         <v>1.2</v>
       </c>
-      <c r="F30" s="22" t="s">
+      <c r="F30" s="21" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="15">
+      <c r="A31" s="11">
         <v>28.0</v>
       </c>
-      <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
       <c r="D31" s="30" t="s">
         <v>86</v>
       </c>
       <c r="E31" s="30">
         <v>3.0</v>
       </c>
-      <c r="F31" s="19" t="s">
+      <c r="F31" s="16" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="15">
+      <c r="A32" s="11">
         <v>29.0</v>
       </c>
-      <c r="B32" s="15"/>
-      <c r="C32" s="15"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
       <c r="D32" s="30" t="s">
         <v>88</v>
       </c>
       <c r="E32" s="30">
         <v>3.0</v>
       </c>
-      <c r="F32" s="19" t="s">
+      <c r="F32" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15">
+      <c r="A33" s="11">
         <v>30.0</v>
       </c>
-      <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
       <c r="D33" s="30" t="s">
         <v>90</v>
       </c>
       <c r="E33" s="30">
         <v>1.5</v>
       </c>
-      <c r="F33" s="19" t="s">
+      <c r="F33" s="16" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="15">
+      <c r="A34" s="11">
         <v>31.0</v>
       </c>
-      <c r="B34" s="15"/>
-      <c r="C34" s="15"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
       <c r="D34" s="30" t="s">
         <v>92</v>
       </c>
       <c r="E34" s="30">
         <v>1.0</v>
       </c>
-      <c r="F34" s="22" t="s">
+      <c r="F34" s="21" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="15">
+      <c r="A35" s="11">
         <v>32.0</v>
       </c>
-      <c r="B35" s="15"/>
-      <c r="C35" s="15"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
       <c r="D35" s="30" t="s">
         <v>94</v>
       </c>
       <c r="E35" s="30">
         <v>0.6</v>
       </c>
-      <c r="F35" s="22" t="s">
+      <c r="F35" s="21" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="15">
+      <c r="A36" s="11">
         <v>33.0</v>
       </c>
-      <c r="B36" s="15"/>
-      <c r="C36" s="15"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
       <c r="D36" s="30" t="s">
         <v>96</v>
       </c>
       <c r="E36" s="30">
         <v>6.0</v>
       </c>
-      <c r="F36" s="19" t="s">
+      <c r="F36" s="16" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="15">
+      <c r="A37" s="11">
         <v>34.0</v>
       </c>
-      <c r="B37" s="15"/>
-      <c r="C37" s="15"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
       <c r="D37" s="30" t="s">
         <v>98</v>
       </c>
       <c r="E37" s="30">
         <v>1.0</v>
       </c>
-      <c r="F37" s="22" t="s">
+      <c r="F37" s="21" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="15">
+      <c r="A38" s="11">
         <v>35.0</v>
       </c>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
       <c r="D38" s="30" t="s">
         <v>100</v>
       </c>
       <c r="E38" s="30">
         <v>1.5</v>
       </c>
-      <c r="F38" s="22" t="s">
+      <c r="F38" s="21" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="15">
+      <c r="A39" s="11">
         <v>36.0</v>
       </c>
-      <c r="B39" s="15"/>
-      <c r="C39" s="15"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
       <c r="D39" s="30" t="s">
         <v>102</v>
       </c>
       <c r="E39" s="30">
         <v>2.0</v>
       </c>
-      <c r="F39" s="22" t="s">
+      <c r="F39" s="21" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="15">
+      <c r="A40" s="11">
         <v>37.0</v>
       </c>
-      <c r="B40" s="15"/>
-      <c r="C40" s="15"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
       <c r="D40" s="30" t="s">
         <v>104</v>
       </c>
       <c r="E40" s="30">
         <v>1.5</v>
       </c>
-      <c r="F40" s="19" t="s">
+      <c r="F40" s="16" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="15">
+      <c r="A41" s="11">
         <v>39.0</v>
       </c>
-      <c r="B41" s="15">
+      <c r="B41" s="11">
         <v>2.5125085E7</v>
       </c>
-      <c r="C41" s="15" t="s">
+      <c r="C41" s="11" t="s">
         <v>48</v>
       </c>
       <c r="D41" s="33" t="s">
@@ -6142,12 +6147,12 @@
       <c r="E41" s="33">
         <v>1.0</v>
       </c>
-      <c r="F41" s="22" t="s">
+      <c r="F41" s="21" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="15">
+      <c r="A42" s="11">
         <v>40.0</v>
       </c>
       <c r="B42" s="34"/>
@@ -6158,12 +6163,12 @@
       <c r="E42" s="33">
         <v>2.0</v>
       </c>
-      <c r="F42" s="22" t="s">
+      <c r="F42" s="21" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="15">
+      <c r="A43" s="11">
         <v>41.0</v>
       </c>
       <c r="B43" s="34"/>
@@ -6171,15 +6176,15 @@
       <c r="D43" s="36" t="s">
         <v>110</v>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="11">
         <v>1.5</v>
       </c>
-      <c r="F43" s="22" t="s">
+      <c r="F43" s="21" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="15">
+      <c r="A44" s="11">
         <v>42.0</v>
       </c>
       <c r="B44" s="34"/>
@@ -6187,15 +6192,15 @@
       <c r="D44" s="36" t="s">
         <v>112</v>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="11">
         <v>1.5</v>
       </c>
-      <c r="F44" s="19" t="s">
+      <c r="F44" s="16" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="15">
+      <c r="A45" s="11">
         <v>43.0</v>
       </c>
       <c r="B45" s="34"/>
@@ -6203,15 +6208,15 @@
       <c r="D45" s="36" t="s">
         <v>114</v>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="11">
         <v>3.0</v>
       </c>
-      <c r="F45" s="19" t="s">
+      <c r="F45" s="16" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="15">
+      <c r="A46" s="11">
         <v>44.0</v>
       </c>
       <c r="B46" s="34"/>
@@ -6219,15 +6224,15 @@
       <c r="D46" s="36" t="s">
         <v>116</v>
       </c>
-      <c r="E46" s="15">
+      <c r="E46" s="11">
         <v>1.0</v>
       </c>
-      <c r="F46" s="22" t="s">
+      <c r="F46" s="21" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="15">
+      <c r="A47" s="11">
         <v>45.0</v>
       </c>
       <c r="B47" s="34"/>
@@ -6235,15 +6240,15 @@
       <c r="D47" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="E47" s="15">
+      <c r="E47" s="11">
         <v>0.5</v>
       </c>
-      <c r="F47" s="22" t="s">
+      <c r="F47" s="21" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="15">
+      <c r="A48" s="11">
         <v>46.0</v>
       </c>
       <c r="B48" s="34"/>
@@ -6251,15 +6256,15 @@
       <c r="D48" s="36" t="s">
         <v>119</v>
       </c>
-      <c r="E48" s="15">
+      <c r="E48" s="11">
         <v>1.0</v>
       </c>
-      <c r="F48" s="22" t="s">
+      <c r="F48" s="21" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="15">
+      <c r="A49" s="11">
         <v>47.0</v>
       </c>
       <c r="B49" s="34"/>
@@ -6267,15 +6272,15 @@
       <c r="D49" s="36" t="s">
         <v>121</v>
       </c>
-      <c r="E49" s="15">
+      <c r="E49" s="11">
         <v>1.0</v>
       </c>
-      <c r="F49" s="22" t="s">
+      <c r="F49" s="21" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="15">
+      <c r="A50" s="11">
         <v>48.0</v>
       </c>
       <c r="B50" s="34"/>
@@ -6283,15 +6288,15 @@
       <c r="D50" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="E50" s="15">
+      <c r="E50" s="11">
         <v>2.0</v>
       </c>
-      <c r="F50" s="22" t="s">
+      <c r="F50" s="21" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="15">
+      <c r="A51" s="11">
         <v>49.0</v>
       </c>
       <c r="B51" s="34"/>
@@ -6299,15 +6304,15 @@
       <c r="D51" s="36" t="s">
         <v>125</v>
       </c>
-      <c r="E51" s="15">
+      <c r="E51" s="11">
         <v>0.5</v>
       </c>
-      <c r="F51" s="22" t="s">
+      <c r="F51" s="21" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="15">
+      <c r="A52" s="11">
         <v>50.0</v>
       </c>
       <c r="B52" s="34"/>
@@ -6315,15 +6320,15 @@
       <c r="D52" s="36" t="s">
         <v>127</v>
       </c>
-      <c r="E52" s="15">
+      <c r="E52" s="11">
         <v>1.0</v>
       </c>
-      <c r="F52" s="19" t="s">
+      <c r="F52" s="16" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="18">
+      <c r="A53" s="20">
         <v>51.0</v>
       </c>
       <c r="B53" s="37"/>
@@ -6333,7 +6338,7 @@
       <c r="F53" s="38"/>
     </row>
     <row r="54">
-      <c r="A54" s="18">
+      <c r="A54" s="20">
         <v>52.0</v>
       </c>
       <c r="B54" s="37"/>
@@ -6343,7 +6348,7 @@
       <c r="F54" s="38"/>
     </row>
     <row r="55">
-      <c r="A55" s="18">
+      <c r="A55" s="20">
         <v>53.0</v>
       </c>
       <c r="B55" s="37"/>
@@ -6353,7 +6358,7 @@
       <c r="F55" s="38"/>
     </row>
     <row r="56">
-      <c r="A56" s="18">
+      <c r="A56" s="20">
         <v>54.0</v>
       </c>
       <c r="B56" s="37"/>
@@ -6363,7 +6368,7 @@
       <c r="F56" s="38"/>
     </row>
     <row r="57">
-      <c r="A57" s="18">
+      <c r="A57" s="20">
         <v>55.0</v>
       </c>
       <c r="B57" s="37"/>
@@ -6373,7 +6378,7 @@
       <c r="F57" s="38"/>
     </row>
     <row r="58">
-      <c r="A58" s="18">
+      <c r="A58" s="20">
         <v>56.0</v>
       </c>
       <c r="B58" s="37"/>
@@ -6383,7 +6388,7 @@
       <c r="F58" s="38"/>
     </row>
     <row r="59">
-      <c r="A59" s="18">
+      <c r="A59" s="20">
         <v>57.0</v>
       </c>
       <c r="B59" s="37"/>
@@ -6393,7 +6398,7 @@
       <c r="F59" s="38"/>
     </row>
     <row r="60">
-      <c r="A60" s="18">
+      <c r="A60" s="20">
         <v>58.0</v>
       </c>
       <c r="B60" s="37"/>
@@ -6403,7 +6408,7 @@
       <c r="F60" s="38"/>
     </row>
     <row r="61">
-      <c r="A61" s="18">
+      <c r="A61" s="20">
         <v>59.0</v>
       </c>
       <c r="B61" s="37"/>
@@ -6413,7 +6418,7 @@
       <c r="F61" s="38"/>
     </row>
     <row r="62">
-      <c r="A62" s="18">
+      <c r="A62" s="20">
         <v>60.0</v>
       </c>
       <c r="B62" s="37"/>
@@ -6423,7 +6428,7 @@
       <c r="F62" s="38"/>
     </row>
     <row r="63">
-      <c r="A63" s="18">
+      <c r="A63" s="20">
         <v>61.0</v>
       </c>
       <c r="B63" s="37"/>
@@ -6433,7 +6438,7 @@
       <c r="F63" s="38"/>
     </row>
     <row r="64">
-      <c r="A64" s="18">
+      <c r="A64" s="20">
         <v>62.0</v>
       </c>
       <c r="B64" s="37"/>
@@ -6443,7 +6448,7 @@
       <c r="F64" s="38"/>
     </row>
     <row r="65">
-      <c r="A65" s="18">
+      <c r="A65" s="20">
         <v>63.0</v>
       </c>
       <c r="B65" s="37"/>
@@ -6453,7 +6458,7 @@
       <c r="F65" s="38"/>
     </row>
     <row r="66">
-      <c r="A66" s="18">
+      <c r="A66" s="20">
         <v>64.0</v>
       </c>
       <c r="B66" s="37"/>
@@ -6463,7 +6468,7 @@
       <c r="F66" s="38"/>
     </row>
     <row r="67">
-      <c r="A67" s="18">
+      <c r="A67" s="20">
         <v>65.0</v>
       </c>
       <c r="B67" s="37"/>
@@ -6473,7 +6478,7 @@
       <c r="F67" s="38"/>
     </row>
     <row r="68">
-      <c r="A68" s="18">
+      <c r="A68" s="20">
         <v>66.0</v>
       </c>
       <c r="B68" s="37"/>
@@ -6483,7 +6488,7 @@
       <c r="F68" s="38"/>
     </row>
     <row r="69">
-      <c r="A69" s="18">
+      <c r="A69" s="20">
         <v>67.0</v>
       </c>
       <c r="B69" s="37"/>
@@ -6493,7 +6498,7 @@
       <c r="F69" s="38"/>
     </row>
     <row r="70">
-      <c r="A70" s="18">
+      <c r="A70" s="20">
         <v>68.0</v>
       </c>
       <c r="B70" s="37"/>
@@ -6503,7 +6508,7 @@
       <c r="F70" s="38"/>
     </row>
     <row r="71">
-      <c r="A71" s="18">
+      <c r="A71" s="20">
         <v>69.0</v>
       </c>
       <c r="B71" s="37"/>
@@ -6513,7 +6518,7 @@
       <c r="F71" s="38"/>
     </row>
     <row r="72">
-      <c r="A72" s="18">
+      <c r="A72" s="20">
         <v>70.0</v>
       </c>
       <c r="B72" s="37"/>
@@ -6523,7 +6528,7 @@
       <c r="F72" s="38"/>
     </row>
     <row r="73">
-      <c r="A73" s="18">
+      <c r="A73" s="20">
         <v>71.0</v>
       </c>
       <c r="B73" s="37"/>
@@ -6533,7 +6538,7 @@
       <c r="F73" s="38"/>
     </row>
     <row r="74">
-      <c r="A74" s="18">
+      <c r="A74" s="20">
         <v>72.0</v>
       </c>
       <c r="B74" s="37"/>
@@ -6543,7 +6548,7 @@
       <c r="F74" s="38"/>
     </row>
     <row r="75">
-      <c r="A75" s="18">
+      <c r="A75" s="20">
         <v>73.0</v>
       </c>
       <c r="B75" s="37"/>
@@ -6553,7 +6558,7 @@
       <c r="F75" s="38"/>
     </row>
     <row r="76">
-      <c r="A76" s="18">
+      <c r="A76" s="20">
         <v>74.0</v>
       </c>
       <c r="B76" s="37"/>
@@ -6563,7 +6568,7 @@
       <c r="F76" s="38"/>
     </row>
     <row r="77">
-      <c r="A77" s="18">
+      <c r="A77" s="20">
         <v>75.0</v>
       </c>
       <c r="B77" s="37"/>
@@ -6573,7 +6578,7 @@
       <c r="F77" s="38"/>
     </row>
     <row r="78">
-      <c r="A78" s="18">
+      <c r="A78" s="20">
         <v>76.0</v>
       </c>
       <c r="B78" s="37"/>
@@ -6583,7 +6588,7 @@
       <c r="F78" s="38"/>
     </row>
     <row r="79">
-      <c r="A79" s="18">
+      <c r="A79" s="20">
         <v>77.0</v>
       </c>
       <c r="B79" s="37"/>
@@ -6593,7 +6598,7 @@
       <c r="F79" s="38"/>
     </row>
     <row r="80">
-      <c r="A80" s="18">
+      <c r="A80" s="20">
         <v>78.0</v>
       </c>
       <c r="B80" s="37"/>
@@ -6603,7 +6608,7 @@
       <c r="F80" s="38"/>
     </row>
     <row r="81">
-      <c r="A81" s="18">
+      <c r="A81" s="20">
         <v>79.0</v>
       </c>
       <c r="B81" s="37"/>
@@ -6613,7 +6618,7 @@
       <c r="F81" s="38"/>
     </row>
     <row r="82">
-      <c r="A82" s="18">
+      <c r="A82" s="20">
         <v>80.0</v>
       </c>
       <c r="B82" s="37"/>
@@ -6623,7 +6628,7 @@
       <c r="F82" s="38"/>
     </row>
     <row r="83">
-      <c r="A83" s="18">
+      <c r="A83" s="20">
         <v>81.0</v>
       </c>
       <c r="B83" s="37"/>
@@ -6633,7 +6638,7 @@
       <c r="F83" s="38"/>
     </row>
     <row r="84">
-      <c r="A84" s="18">
+      <c r="A84" s="20">
         <v>82.0</v>
       </c>
       <c r="B84" s="37"/>
@@ -6643,7 +6648,7 @@
       <c r="F84" s="38"/>
     </row>
     <row r="85">
-      <c r="A85" s="18">
+      <c r="A85" s="20">
         <v>83.0</v>
       </c>
       <c r="B85" s="37"/>
@@ -6653,7 +6658,7 @@
       <c r="F85" s="38"/>
     </row>
     <row r="86">
-      <c r="A86" s="18">
+      <c r="A86" s="20">
         <v>84.0</v>
       </c>
       <c r="B86" s="37"/>
@@ -6663,7 +6668,7 @@
       <c r="F86" s="38"/>
     </row>
     <row r="87">
-      <c r="A87" s="18">
+      <c r="A87" s="20">
         <v>85.0</v>
       </c>
       <c r="B87" s="37"/>
@@ -6673,7 +6678,7 @@
       <c r="F87" s="38"/>
     </row>
     <row r="88">
-      <c r="A88" s="18">
+      <c r="A88" s="20">
         <v>86.0</v>
       </c>
       <c r="B88" s="37"/>
@@ -6683,7 +6688,7 @@
       <c r="F88" s="38"/>
     </row>
     <row r="89">
-      <c r="A89" s="18">
+      <c r="A89" s="20">
         <v>87.0</v>
       </c>
       <c r="B89" s="37"/>
@@ -6693,7 +6698,7 @@
       <c r="F89" s="38"/>
     </row>
     <row r="90">
-      <c r="A90" s="18">
+      <c r="A90" s="20">
         <v>88.0</v>
       </c>
       <c r="B90" s="37"/>
@@ -6703,7 +6708,7 @@
       <c r="F90" s="38"/>
     </row>
     <row r="91">
-      <c r="A91" s="18">
+      <c r="A91" s="20">
         <v>89.0</v>
       </c>
       <c r="B91" s="37"/>
@@ -6713,7 +6718,7 @@
       <c r="F91" s="38"/>
     </row>
     <row r="92">
-      <c r="A92" s="18">
+      <c r="A92" s="20">
         <v>90.0</v>
       </c>
       <c r="B92" s="37"/>
@@ -6723,7 +6728,7 @@
       <c r="F92" s="38"/>
     </row>
     <row r="93">
-      <c r="A93" s="18">
+      <c r="A93" s="20">
         <v>91.0</v>
       </c>
       <c r="B93" s="37"/>
@@ -6733,7 +6738,7 @@
       <c r="F93" s="38"/>
     </row>
     <row r="94">
-      <c r="A94" s="18">
+      <c r="A94" s="20">
         <v>92.0</v>
       </c>
       <c r="B94" s="37"/>
@@ -6743,7 +6748,7 @@
       <c r="F94" s="38"/>
     </row>
     <row r="95">
-      <c r="A95" s="18">
+      <c r="A95" s="20">
         <v>93.0</v>
       </c>
       <c r="B95" s="37"/>
@@ -6753,7 +6758,7 @@
       <c r="F95" s="38"/>
     </row>
     <row r="96">
-      <c r="A96" s="18">
+      <c r="A96" s="20">
         <v>94.0</v>
       </c>
       <c r="B96" s="37"/>
@@ -6763,7 +6768,7 @@
       <c r="F96" s="38"/>
     </row>
     <row r="97">
-      <c r="A97" s="18">
+      <c r="A97" s="20">
         <v>95.0</v>
       </c>
       <c r="B97" s="37"/>
@@ -6773,7 +6778,7 @@
       <c r="F97" s="38"/>
     </row>
     <row r="98">
-      <c r="A98" s="18">
+      <c r="A98" s="20">
         <v>96.0</v>
       </c>
       <c r="B98" s="37"/>
@@ -6783,7 +6788,7 @@
       <c r="F98" s="38"/>
     </row>
     <row r="99">
-      <c r="A99" s="18">
+      <c r="A99" s="20">
         <v>97.0</v>
       </c>
       <c r="B99" s="37"/>
@@ -6793,7 +6798,7 @@
       <c r="F99" s="38"/>
     </row>
     <row r="100">
-      <c r="A100" s="18">
+      <c r="A100" s="20">
         <v>98.0</v>
       </c>
       <c r="B100" s="37"/>
@@ -6803,7 +6808,7 @@
       <c r="F100" s="38"/>
     </row>
     <row r="101">
-      <c r="A101" s="18">
+      <c r="A101" s="20">
         <v>99.0</v>
       </c>
       <c r="B101" s="37"/>
@@ -6813,7 +6818,7 @@
       <c r="F101" s="38"/>
     </row>
     <row r="102">
-      <c r="A102" s="18">
+      <c r="A102" s="20">
         <v>100.0</v>
       </c>
       <c r="B102" s="37"/>
@@ -6823,7 +6828,7 @@
       <c r="F102" s="38"/>
     </row>
     <row r="103">
-      <c r="A103" s="18">
+      <c r="A103" s="20">
         <v>101.0</v>
       </c>
       <c r="B103" s="37"/>
@@ -6833,7 +6838,7 @@
       <c r="F103" s="38"/>
     </row>
     <row r="104">
-      <c r="A104" s="18">
+      <c r="A104" s="20">
         <v>102.0</v>
       </c>
       <c r="B104" s="37"/>
@@ -6843,7 +6848,7 @@
       <c r="F104" s="38"/>
     </row>
     <row r="105">
-      <c r="A105" s="18">
+      <c r="A105" s="20">
         <v>103.0</v>
       </c>
       <c r="B105" s="37"/>
@@ -6853,7 +6858,7 @@
       <c r="F105" s="38"/>
     </row>
     <row r="106">
-      <c r="A106" s="18">
+      <c r="A106" s="20">
         <v>104.0</v>
       </c>
       <c r="B106" s="37"/>
@@ -6863,7 +6868,7 @@
       <c r="F106" s="38"/>
     </row>
     <row r="107">
-      <c r="A107" s="18">
+      <c r="A107" s="20">
         <v>105.0</v>
       </c>
       <c r="B107" s="37"/>
@@ -6873,7 +6878,7 @@
       <c r="F107" s="38"/>
     </row>
     <row r="108">
-      <c r="A108" s="18">
+      <c r="A108" s="20">
         <v>106.0</v>
       </c>
       <c r="B108" s="37"/>
@@ -6883,7 +6888,7 @@
       <c r="F108" s="38"/>
     </row>
     <row r="109">
-      <c r="A109" s="18">
+      <c r="A109" s="20">
         <v>107.0</v>
       </c>
       <c r="B109" s="37"/>
@@ -6893,7 +6898,7 @@
       <c r="F109" s="38"/>
     </row>
     <row r="110">
-      <c r="A110" s="18">
+      <c r="A110" s="20">
         <v>108.0</v>
       </c>
       <c r="B110" s="37"/>
@@ -6903,7 +6908,7 @@
       <c r="F110" s="38"/>
     </row>
     <row r="111">
-      <c r="A111" s="18">
+      <c r="A111" s="20">
         <v>109.0</v>
       </c>
       <c r="B111" s="37"/>
@@ -6913,7 +6918,7 @@
       <c r="F111" s="38"/>
     </row>
     <row r="112">
-      <c r="A112" s="18">
+      <c r="A112" s="20">
         <v>110.0</v>
       </c>
       <c r="B112" s="37"/>
@@ -6923,7 +6928,7 @@
       <c r="F112" s="38"/>
     </row>
     <row r="113">
-      <c r="A113" s="18">
+      <c r="A113" s="20">
         <v>111.0</v>
       </c>
       <c r="B113" s="37"/>
@@ -6933,7 +6938,7 @@
       <c r="F113" s="38"/>
     </row>
     <row r="114">
-      <c r="A114" s="18">
+      <c r="A114" s="20">
         <v>112.0</v>
       </c>
       <c r="B114" s="37"/>
@@ -6943,7 +6948,7 @@
       <c r="F114" s="38"/>
     </row>
     <row r="115">
-      <c r="A115" s="18">
+      <c r="A115" s="20">
         <v>113.0</v>
       </c>
       <c r="B115" s="37"/>
@@ -6953,7 +6958,7 @@
       <c r="F115" s="38"/>
     </row>
     <row r="116">
-      <c r="A116" s="18">
+      <c r="A116" s="20">
         <v>114.0</v>
       </c>
       <c r="B116" s="37"/>
@@ -6963,7 +6968,7 @@
       <c r="F116" s="38"/>
     </row>
     <row r="117">
-      <c r="A117" s="18">
+      <c r="A117" s="20">
         <v>115.0</v>
       </c>
       <c r="B117" s="37"/>
@@ -6973,7 +6978,7 @@
       <c r="F117" s="38"/>
     </row>
     <row r="118">
-      <c r="A118" s="18">
+      <c r="A118" s="20">
         <v>116.0</v>
       </c>
       <c r="B118" s="37"/>
@@ -6983,7 +6988,7 @@
       <c r="F118" s="38"/>
     </row>
     <row r="119">
-      <c r="A119" s="18">
+      <c r="A119" s="20">
         <v>117.0</v>
       </c>
       <c r="B119" s="37"/>
@@ -6993,7 +6998,7 @@
       <c r="F119" s="38"/>
     </row>
     <row r="120">
-      <c r="A120" s="18">
+      <c r="A120" s="20">
         <v>118.0</v>
       </c>
       <c r="B120" s="37"/>
@@ -7003,7 +7008,7 @@
       <c r="F120" s="38"/>
     </row>
     <row r="121">
-      <c r="A121" s="18">
+      <c r="A121" s="20">
         <v>119.0</v>
       </c>
       <c r="B121" s="37"/>
@@ -7013,7 +7018,7 @@
       <c r="F121" s="38"/>
     </row>
     <row r="122">
-      <c r="A122" s="18">
+      <c r="A122" s="20">
         <v>120.0</v>
       </c>
       <c r="B122" s="37"/>
@@ -7023,7 +7028,7 @@
       <c r="F122" s="38"/>
     </row>
     <row r="123">
-      <c r="A123" s="18">
+      <c r="A123" s="20">
         <v>121.0</v>
       </c>
       <c r="B123" s="37"/>
@@ -7033,7 +7038,7 @@
       <c r="F123" s="38"/>
     </row>
     <row r="124">
-      <c r="A124" s="18">
+      <c r="A124" s="20">
         <v>122.0</v>
       </c>
       <c r="B124" s="37"/>
@@ -7043,7 +7048,7 @@
       <c r="F124" s="38"/>
     </row>
     <row r="125">
-      <c r="A125" s="18">
+      <c r="A125" s="20">
         <v>123.0</v>
       </c>
       <c r="B125" s="37"/>
@@ -7053,7 +7058,7 @@
       <c r="F125" s="38"/>
     </row>
     <row r="126">
-      <c r="A126" s="18">
+      <c r="A126" s="20">
         <v>124.0</v>
       </c>
       <c r="B126" s="37"/>
@@ -7063,7 +7068,7 @@
       <c r="F126" s="38"/>
     </row>
     <row r="127">
-      <c r="A127" s="18">
+      <c r="A127" s="20">
         <v>125.0</v>
       </c>
       <c r="B127" s="37"/>
@@ -7073,7 +7078,7 @@
       <c r="F127" s="38"/>
     </row>
     <row r="128">
-      <c r="A128" s="18">
+      <c r="A128" s="20">
         <v>126.0</v>
       </c>
       <c r="B128" s="37"/>
@@ -7083,7 +7088,7 @@
       <c r="F128" s="38"/>
     </row>
     <row r="129">
-      <c r="A129" s="18">
+      <c r="A129" s="20">
         <v>127.0</v>
       </c>
       <c r="B129" s="37"/>
@@ -7093,7 +7098,7 @@
       <c r="F129" s="38"/>
     </row>
     <row r="130">
-      <c r="A130" s="18">
+      <c r="A130" s="20">
         <v>128.0</v>
       </c>
       <c r="B130" s="37"/>
@@ -7103,7 +7108,7 @@
       <c r="F130" s="38"/>
     </row>
     <row r="131">
-      <c r="A131" s="18">
+      <c r="A131" s="20">
         <v>129.0</v>
       </c>
       <c r="B131" s="37"/>
@@ -7113,7 +7118,7 @@
       <c r="F131" s="38"/>
     </row>
     <row r="132">
-      <c r="A132" s="18">
+      <c r="A132" s="20">
         <v>130.0</v>
       </c>
       <c r="B132" s="37"/>
@@ -7123,7 +7128,7 @@
       <c r="F132" s="38"/>
     </row>
     <row r="133">
-      <c r="A133" s="18">
+      <c r="A133" s="20">
         <v>131.0</v>
       </c>
       <c r="B133" s="37"/>
@@ -7133,7 +7138,7 @@
       <c r="F133" s="38"/>
     </row>
     <row r="134">
-      <c r="A134" s="18">
+      <c r="A134" s="20">
         <v>132.0</v>
       </c>
       <c r="B134" s="37"/>
@@ -7143,7 +7148,7 @@
       <c r="F134" s="38"/>
     </row>
     <row r="135">
-      <c r="A135" s="18">
+      <c r="A135" s="20">
         <v>133.0</v>
       </c>
       <c r="B135" s="37"/>
@@ -7153,7 +7158,7 @@
       <c r="F135" s="38"/>
     </row>
     <row r="136">
-      <c r="A136" s="18">
+      <c r="A136" s="20">
         <v>134.0</v>
       </c>
       <c r="B136" s="37"/>
@@ -9914,6 +9919,9 @@
     <hyperlink r:id="rId48" ref="F51"/>
     <hyperlink r:id="rId49" ref="F52"/>
   </hyperlinks>
+  <printOptions gridLines="1" horizontalCentered="1"/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup fitToHeight="0" cellComments="atEnd" orientation="landscape" pageOrder="overThenDown"/>
   <drawing r:id="rId50"/>
   <tableParts count="1">
     <tablePart r:id="rId52"/>
